--- a/data/interim/hplc_rt_solubility_updated.xlsx
+++ b/data/interim/hplc_rt_solubility_updated.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1101"/>
+  <dimension ref="A1:L1108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col width="7.90625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -53231,6 +53231,342 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>PFP</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>L-proline</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>147-85-3</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>matrix ID PFP 1</t>
+        </is>
+      </c>
+      <c r="H1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>2-amino-4,6-dihydroxypyrimidine</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>56-09-7</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>L-Cystine</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>56-89-3</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>caffeine</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>58-08-2</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>triphenylphospine</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>603-35-0</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>BlueBird</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Indol acetic acid</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>87-51-4</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>matrix ID BlueBird 1</t>
+        </is>
+      </c>
+      <c r="H1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>PFP</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>method_1</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2-2-bis(diphenylphosphino)1.1-binaphthyl</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>98327-87-8</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>6.786</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>matrix ID PFP 1</t>
+        </is>
+      </c>
+      <c r="H1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1108" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
